--- a/HW/FT8_RP2040_TRX/Project Outputs/Fabrication/BOM/FT8.xlsx
+++ b/HW/FT8_RP2040_TRX/Project Outputs/Fabrication/BOM/FT8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\donke\Documents\Projets\RP2040_FT8_TRX\HW\FT8_RP2040_TRX\Project Outputs\Fabrication\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A995FA56-DC2C-4630-9453-B4828FA62003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{140E3589-0F64-4E7F-B104-957597DAB288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7680" yWindow="960" windowWidth="23040" windowHeight="13560" xr2:uid="{970E3DF8-C563-4041-B3D2-5C176CFF1ADD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{22B7EBD4-85BD-4460-9FFD-37089B6CC9F4}"/>
   </bookViews>
   <sheets>
     <sheet name="FT8" sheetId="1" r:id="rId1"/>
@@ -252,7 +252,7 @@
     <t>FKP2O111001I00HC00-Footprint-1</t>
   </si>
   <si>
-    <t>C20, C25</t>
+    <t>C20</t>
   </si>
   <si>
     <t>FKP2D002201D00HA00</t>
@@ -363,7 +363,7 @@
     <t>C0603C220J4GAC7867</t>
   </si>
   <si>
-    <t>C43, C44</t>
+    <t>C43, C44, C70, C71, C72</t>
   </si>
   <si>
     <t>10 nF 10% 50 V 0603</t>
@@ -801,7 +801,7 @@
     <t>0603WAJ0270T5E</t>
   </si>
   <si>
-    <t>R12, R13, R23, R26</t>
+    <t>R12, R13, R23, R26, R29, R30, R31, R32, R33</t>
   </si>
   <si>
     <t>10K 1% 0.1W 0603</t>
@@ -822,7 +822,7 @@
     <t>0603WAF5101T5E</t>
   </si>
   <si>
-    <t>R17, R27, R28</t>
+    <t>R17</t>
   </si>
   <si>
     <t>2K 1% 0.1W 0603</t>
@@ -867,7 +867,7 @@
     <t>RESC3116X70X50ML13T20</t>
   </si>
   <si>
-    <t>SW1, SW2</t>
+    <t>SW1, SW2, SW3, SW4, SW5</t>
   </si>
   <si>
     <t>SKRPASE010</t>
@@ -1510,7 +1510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F0F2ED-2780-4C61-9AA5-BCF492DD7633}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06461D8D-B5BC-4D8C-9753-23EE772FB23E}">
   <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1833,7 +1833,7 @@
         <v>73</v>
       </c>
       <c r="E12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -2031,7 +2031,7 @@
         <v>26</v>
       </c>
       <c r="E20" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>114</v>
@@ -2756,7 +2756,7 @@
         <v>217</v>
       </c>
       <c r="E47" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>224</v>
@@ -2810,7 +2810,7 @@
         <v>217</v>
       </c>
       <c r="E49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>267</v>
@@ -2885,7 +2885,7 @@
         <v>280</v>
       </c>
       <c r="E52" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>282</v>
